--- a/mainWidget/mainWidget/src/database/计算模型-跌落试验-90.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-跌落试验-90.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E357278E-AB11-471B-A28C-1B73266936FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD03042-FA0C-46D4-A225-E2E1AC7544FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="1372">
   <si>
     <t>序号</t>
   </si>
@@ -308,1505 +308,4224 @@
   </si>
   <si>
     <t>-83.7199</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-453.9937</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-140.4314</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>147.4787</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-172.3491</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-31.9235</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-27.4376</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-42.71</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8676.8431</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>139.7315</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-131.6773</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-8690.4683</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-459.4851</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-97.6613</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-47.0605</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-51.2095</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-52.9808</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-300.6598</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-348.3307</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-62.7115</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-42.7693</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-53.4826</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3592.0102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-350.0945</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-63.0886</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-43.4964</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-53.0956</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3583.3128</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-115.6633</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-48.7106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-51.0877</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-52.6296</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-293.2695</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-186.0024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.1425</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-27.5968</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-467.2983</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-43.4687</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-61.062</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-456.1983</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2587</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0635</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.036</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0353</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0156</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0174</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0265</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0181</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0035</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0417</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0406</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0173</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0168</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2585</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0633</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0362</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0356</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2385</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3451</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6501</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1942</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>5.9651</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0236</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0326</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0186</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3411</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0456</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0094</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2099</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8184</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0478</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0319</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0503</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2048</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>5.8732</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2248</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6281</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3076</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1999</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3441</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0169</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0313</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0207</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0138</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1832</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4365</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2722</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0446</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0309</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0481</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8429</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0853</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0414</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0053</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0404</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0077</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0175</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.135</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0051</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0536</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1408</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0045</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0544</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0461</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0074</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0207</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0033</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0069</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0519</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.084</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0435</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0162</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2654</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.269</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1327</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0346</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1783</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0076</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0067</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0078</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0745</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1254</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0113</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0087</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0685</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0654</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5998</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0671</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1242</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0084</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0636</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1756</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0075</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0066</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0736</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.2614</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2681</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0333</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0059</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.3005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.298</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.8501</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6584</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8067</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1706</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.3758</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6088</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1182</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2074</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0144</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.5093</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.1278</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0083</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3152</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2691</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7521</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.9038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1406</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1634</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0731</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6672</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.8347</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6602</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-10.9112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.6638</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0107</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2082</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1156</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2745</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.3079</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0137</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.0699</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.6158</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.6626</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0641</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1906</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1343</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.6824</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0145</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.037</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0312</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0699</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9325</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0065</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0041</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0081</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0068</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0831</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0048</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2678</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0822</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0057</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.9346</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0363</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0329</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0042</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0059</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0316</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1523</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0093</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0131</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0143</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0592</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0203</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0588</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0142</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1527</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0803</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.2029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5878</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4.3637</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0656</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0219</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.146</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0826</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.0945</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0789</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.0827</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0028</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1477</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0582</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0135</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1964</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.0928</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0495</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1972</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5853</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>4.3595</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4517</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.3739</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4154</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4561</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>30.5971</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9063</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0771</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0175</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.1416</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.0836</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1259</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0489</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.115</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.1614</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.2686</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1511</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0657</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1193</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>11.9058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>3.2719</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1525</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0667</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.1201</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>11.8565</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.082</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.128</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.1669</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.9134</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0777</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0501</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>2.1274</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4459</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>30.645</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.4655</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.4127</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1.3952</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-109.2879</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.7582</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-33.0194</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.6181</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-47.6946</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.5026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4439</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0197</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-13.1781</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-43.7177</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.077</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.193</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.2026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-11.5412</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-320.0872</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.1677</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7966</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.3585</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-23.3839</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-322.7872</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.1234</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.7479</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.2692</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-23.345</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-44.2718</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.037</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.1836</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-1.1702</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-12.1365</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-47.9075</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4809</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-0.4156</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0837</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-13.3709</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-678.3831</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-108.8663</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.3423</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-32.3968</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-3.2185</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>-680.732</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0.0092</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>-2834.5646 +0.0413*B + 0.0*C +1.2353*D -0.0168*E +0.3177*F + 0.0*G +0.0816*H -0.0229*I +0.0009*J +0.19*K +3.7598*L -110.0805*M</t>
+  </si>
+  <si>
+    <t>-2834.5646</t>
+  </si>
+  <si>
+    <t>0.0413</t>
+  </si>
+  <si>
+    <t>1.2353</t>
+  </si>
+  <si>
+    <t>-0.0168</t>
+  </si>
+  <si>
+    <t>0.3177</t>
+  </si>
+  <si>
+    <t>0.0816</t>
+  </si>
+  <si>
+    <t>-0.0229</t>
+  </si>
+  <si>
+    <t>0.0009</t>
+  </si>
+  <si>
+    <t>0.1900</t>
+  </si>
+  <si>
+    <t>3.7598</t>
+  </si>
+  <si>
+    <t>-110.0805</t>
+  </si>
+  <si>
+    <t>-206.6274 +0.01*B + 0.0*C +0.9591*D +0.0063*E +0.1258*F + 0.0*G -1.4921*H +0.0817*I +0.0086*J -0.4009*K +9.5047*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-206.6274</t>
+  </si>
+  <si>
+    <t>0.0100</t>
+  </si>
+  <si>
+    <t>0.9591</t>
+  </si>
+  <si>
+    <t>0.0063</t>
+  </si>
+  <si>
+    <t>0.1258</t>
+  </si>
+  <si>
+    <t>-1.4921</t>
+  </si>
+  <si>
+    <t>0.0817</t>
+  </si>
+  <si>
+    <t>0.0086</t>
+  </si>
+  <si>
+    <t>-0.4009</t>
+  </si>
+  <si>
+    <t>9.5047</t>
+  </si>
+  <si>
+    <t>0.0921</t>
+  </si>
+  <si>
+    <t>-1032.9723 +0.0013*B + 0.0*C +0.4397*D +0.0129*E +0.2735*F + 0.0*G +1.3571*H -0.0937*I +0.0187*J +0.452*K -1.5569*L -138.643*M</t>
+  </si>
+  <si>
+    <t>-1032.9723</t>
+  </si>
+  <si>
+    <t>0.0013</t>
+  </si>
+  <si>
+    <t>0.4397</t>
+  </si>
+  <si>
+    <t>0.0129</t>
+  </si>
+  <si>
+    <t>0.2735</t>
+  </si>
+  <si>
+    <t>1.3571</t>
+  </si>
+  <si>
+    <t>-0.0937</t>
+  </si>
+  <si>
+    <t>0.0187</t>
+  </si>
+  <si>
+    <t>0.4520</t>
+  </si>
+  <si>
+    <t>-1.5569</t>
+  </si>
+  <si>
+    <t>-138.6430</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0551*B + 0.0*C -0.0865*D +0.0192*E +0.0025*F + 0.0*G -2.7341*H -0.2109*I +0.0064*J -0.1145*K +2.7166*L -124.9122*M</t>
+  </si>
+  <si>
+    <t>162.2266</t>
+  </si>
+  <si>
+    <t>0.0551</t>
+  </si>
+  <si>
+    <t>-0.0865</t>
+  </si>
+  <si>
+    <t>0.0192</t>
+  </si>
+  <si>
+    <t>0.0025</t>
+  </si>
+  <si>
+    <t>-2.7341</t>
+  </si>
+  <si>
+    <t>-0.2109</t>
+  </si>
+  <si>
+    <t>0.0064</t>
+  </si>
+  <si>
+    <t>-0.1145</t>
+  </si>
+  <si>
+    <t>2.7166</t>
+  </si>
+  <si>
+    <t>-124.9122</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0012*B + 0.0*C -0.5198*D -0.0016*E +0.0025*F + 0.0*G +1.5214*H -0.2051*I +0.0063*J -0.2875*K -0.8013*L -55.8049*M</t>
+  </si>
+  <si>
+    <t>0.0012</t>
+  </si>
+  <si>
+    <t>-0.5198</t>
+  </si>
+  <si>
+    <t>-0.0016</t>
+  </si>
+  <si>
+    <t>1.5214</t>
+  </si>
+  <si>
+    <t>-0.2051</t>
+  </si>
+  <si>
+    <t>-0.2875</t>
+  </si>
+  <si>
+    <t>-0.8013</t>
+  </si>
+  <si>
+    <t>-55.8049</t>
+  </si>
+  <si>
+    <t>-119.2519 +0.0012*B + 0.0*C +1.3146*D -0.0125*E +0.0025*F + 0.0*G -2.0197*H -0.0491*I +0.0225*J +0.3192*K -1.5569*L -166.2033*M</t>
+  </si>
+  <si>
+    <t>-119.2519</t>
+  </si>
+  <si>
+    <t>1.3146</t>
+  </si>
+  <si>
+    <t>-0.0125</t>
+  </si>
+  <si>
+    <t>-2.0197</t>
+  </si>
+  <si>
+    <t>-0.0491</t>
+  </si>
+  <si>
+    <t>0.0225</t>
+  </si>
+  <si>
+    <t>0.3192</t>
+  </si>
+  <si>
+    <t>-166.2033</t>
+  </si>
+  <si>
+    <t>7.3133 +0.0546*B + 0.0*C +1.1317*D -0.0463*E +0.0025*F + 0.0*G -0.1413*H -0.0944*I +0.0034*J +1.6049*K +0.3663*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>7.3133</t>
+  </si>
+  <si>
+    <t>0.0546</t>
+  </si>
+  <si>
+    <t>1.1317</t>
+  </si>
+  <si>
+    <t>-0.0463</t>
+  </si>
+  <si>
+    <t>-0.1413</t>
+  </si>
+  <si>
+    <t>-0.0944</t>
+  </si>
+  <si>
+    <t>0.0034</t>
+  </si>
+  <si>
+    <t>1.6049</t>
+  </si>
+  <si>
+    <t>0.3663</t>
+  </si>
+  <si>
+    <t>-2302.0164 +0.0494*B + 0.0*C -0.6193*D +0.0067*E +0.2657*F + 0.0*G -3.0506*H +0.0656*I +0.0336*J +0.583*K +3.1444*L -63.5198*M</t>
+  </si>
+  <si>
+    <t>-2302.0164</t>
+  </si>
+  <si>
+    <t>0.0494</t>
+  </si>
+  <si>
+    <t>-0.6193</t>
+  </si>
+  <si>
+    <t>0.0067</t>
+  </si>
+  <si>
+    <t>0.2657</t>
+  </si>
+  <si>
+    <t>-3.0506</t>
+  </si>
+  <si>
+    <t>0.0656</t>
+  </si>
+  <si>
+    <t>0.0336</t>
+  </si>
+  <si>
+    <t>0.5830</t>
+  </si>
+  <si>
+    <t>3.1444</t>
+  </si>
+  <si>
+    <t>-63.5198</t>
+  </si>
+  <si>
+    <t>-1426.2095 +0.0012*B + 0.0*C -1.1134*D -0.0013*E +0.476*F + 0.0*G -1.2597*H +0.0914*I +0.0176*J +0.2622*K +2.7025*L -83.9415*M</t>
+  </si>
+  <si>
+    <t>-1426.2095</t>
+  </si>
+  <si>
+    <t>-1.1134</t>
+  </si>
+  <si>
+    <t>-0.0013</t>
+  </si>
+  <si>
+    <t>0.4760</t>
+  </si>
+  <si>
+    <t>-1.2597</t>
+  </si>
+  <si>
+    <t>0.0914</t>
+  </si>
+  <si>
+    <t>0.0176</t>
+  </si>
+  <si>
+    <t>0.2622</t>
+  </si>
+  <si>
+    <t>2.7025</t>
+  </si>
+  <si>
+    <t>-83.9415</t>
+  </si>
+  <si>
+    <t>-3721.4603 +0.0012*B + 0.0*C -0.6454*D -0.0848*E +0.1501*F + 0.0*G -1.067*H -0.1097*I +0.0203*J +0.3247*K +4.0225*L -138.266*M</t>
+  </si>
+  <si>
+    <t>-3721.4603</t>
+  </si>
+  <si>
+    <t>-0.6454</t>
+  </si>
+  <si>
+    <t>-0.0848</t>
+  </si>
+  <si>
+    <t>0.1501</t>
+  </si>
+  <si>
+    <t>-1.0670</t>
+  </si>
+  <si>
+    <t>-0.1097</t>
+  </si>
+  <si>
+    <t>0.0203</t>
+  </si>
+  <si>
+    <t>0.3247</t>
+  </si>
+  <si>
+    <t>4.0225</t>
+  </si>
+  <si>
+    <t>-138.2660</t>
+  </si>
+  <si>
+    <t>-2289.2665 +0.033*B + 0.0*C -0.06*D -0.0402*E +0.0796*F + 0.0*G -2.6056*H +0.0914*I +0.0319*J -0.6466*K +2.1181*L -213.7306*M</t>
+  </si>
+  <si>
+    <t>-2289.2665</t>
+  </si>
+  <si>
+    <t>0.0330</t>
+  </si>
+  <si>
+    <t>-0.0600</t>
+  </si>
+  <si>
+    <t>-0.0402</t>
+  </si>
+  <si>
+    <t>0.0796</t>
+  </si>
+  <si>
+    <t>-2.6056</t>
+  </si>
+  <si>
+    <t>0.0319</t>
+  </si>
+  <si>
+    <t>-0.6466</t>
+  </si>
+  <si>
+    <t>2.1181</t>
+  </si>
+  <si>
+    <t>-213.7306</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0012*B + 0.0*C -0.6133*D -0.0165*E +0.0025*F + 0.0*G +0.7361*H -0.054*I +0.036*J +0.7938*K -1.5569*L -180.5337*M</t>
+  </si>
+  <si>
+    <t>-0.6133</t>
+  </si>
+  <si>
+    <t>-0.0165</t>
+  </si>
+  <si>
+    <t>0.7361</t>
+  </si>
+  <si>
+    <t>-0.0540</t>
+  </si>
+  <si>
+    <t>0.0360</t>
+  </si>
+  <si>
+    <t>0.7938</t>
+  </si>
+  <si>
+    <t>-180.5337</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0619*B + 0.0*C -0.712*D -0.0145*E +0.0025*F + 0.0*G -0.53*H +0.0451*I +0.0264*J -0.5897*K -0.0129*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>0.0619</t>
+  </si>
+  <si>
+    <t>-0.7120</t>
+  </si>
+  <si>
+    <t>-0.0145</t>
+  </si>
+  <si>
+    <t>-0.5300</t>
+  </si>
+  <si>
+    <t>0.0451</t>
+  </si>
+  <si>
+    <t>0.0264</t>
+  </si>
+  <si>
+    <t>-0.5897</t>
+  </si>
+  <si>
+    <t>-0.0129</t>
+  </si>
+  <si>
+    <t>-1256.9758 +0.0999*B + 0.0*C +0.006*D -0.0259*E +0.2792*F + 0.0*G -0.402*H -0.0965*I +0.0649*J +0.2054*K +4.6498*L -40.3784*M</t>
+  </si>
+  <si>
+    <t>-1256.9758</t>
+  </si>
+  <si>
+    <t>0.0999</t>
+  </si>
+  <si>
+    <t>0.0060</t>
+  </si>
+  <si>
+    <t>-0.0259</t>
+  </si>
+  <si>
+    <t>0.2792</t>
+  </si>
+  <si>
+    <t>-0.4020</t>
+  </si>
+  <si>
+    <t>-0.0965</t>
+  </si>
+  <si>
+    <t>0.0649</t>
+  </si>
+  <si>
+    <t>0.2054</t>
+  </si>
+  <si>
+    <t>4.6498</t>
+  </si>
+  <si>
+    <t>-40.3784</t>
+  </si>
+  <si>
+    <t>-1114.7019 +0.0012*B + 0.0*C +1.6877*D -0.0286*E +0.3376*F + 0.0*G -1.0379*H -0.0526*I +0.0064*J +0.7896*K -1.5569*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-1114.7019</t>
+  </si>
+  <si>
+    <t>1.6877</t>
+  </si>
+  <si>
+    <t>-0.0286</t>
+  </si>
+  <si>
+    <t>0.3376</t>
+  </si>
+  <si>
+    <t>-1.0379</t>
+  </si>
+  <si>
+    <t>-0.0526</t>
+  </si>
+  <si>
+    <t>0.7896</t>
+  </si>
+  <si>
+    <t>-2470.936 +0.0342*B + 0.0*C +1.068*D -0.0609*E +0.1301*F + 0.0*G -0.2392*H -0.2694*I +0.0222*J -0.1252*K +2.1543*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-2470.9360</t>
+  </si>
+  <si>
+    <t>0.0342</t>
+  </si>
+  <si>
+    <t>1.0680</t>
+  </si>
+  <si>
+    <t>-0.0609</t>
+  </si>
+  <si>
+    <t>0.1301</t>
+  </si>
+  <si>
+    <t>-0.2392</t>
+  </si>
+  <si>
+    <t>-0.2694</t>
+  </si>
+  <si>
+    <t>0.0222</t>
+  </si>
+  <si>
+    <t>-0.1252</t>
+  </si>
+  <si>
+    <t>2.1543</t>
+  </si>
+  <si>
+    <t>-100.9841 +0.0292*B + 0.0*C -0.0535*D -0.0445*E +0.0532*F + 0.0*G -1.0176*H +0.0032*I +0.0009*J +1.0974*K +1.7159*L -133.6707*M</t>
+  </si>
+  <si>
+    <t>-100.9841</t>
+  </si>
+  <si>
+    <t>0.0292</t>
+  </si>
+  <si>
+    <t>-0.0535</t>
+  </si>
+  <si>
+    <t>-0.0445</t>
+  </si>
+  <si>
+    <t>0.0532</t>
+  </si>
+  <si>
+    <t>-1.0176</t>
+  </si>
+  <si>
+    <t>0.0032</t>
+  </si>
+  <si>
+    <t>1.0974</t>
+  </si>
+  <si>
+    <t>1.7159</t>
+  </si>
+  <si>
+    <t>-133.6707</t>
+  </si>
+  <si>
+    <t>-1441.3032 +0.0547*B + 0.0*C +0.6461*D +0.0339*E +0.2349*F + 0.0*G +1.0696*H +0.0914*I +0.0082*J +0.7235*K +1.9497*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-1441.3032</t>
+  </si>
+  <si>
+    <t>0.0547</t>
+  </si>
+  <si>
+    <t>0.6461</t>
+  </si>
+  <si>
+    <t>0.0339</t>
+  </si>
+  <si>
+    <t>0.2349</t>
+  </si>
+  <si>
+    <t>1.0696</t>
+  </si>
+  <si>
+    <t>0.0082</t>
+  </si>
+  <si>
+    <t>0.7235</t>
+  </si>
+  <si>
+    <t>1.9497</t>
+  </si>
+  <si>
+    <t>-1451.6565 +0.083*B + 0.0*C +0.7846*D -0.0332*E +0.2489*F + 0.0*G -1.3503*H -0.0383*I +0.0445*J +1.1933*K -1.5569*L -38.6177*M</t>
+  </si>
+  <si>
+    <t>-1451.6565</t>
+  </si>
+  <si>
+    <t>0.0830</t>
+  </si>
+  <si>
+    <t>0.7846</t>
+  </si>
+  <si>
+    <t>-0.0332</t>
+  </si>
+  <si>
+    <t>0.2489</t>
+  </si>
+  <si>
+    <t>-1.3503</t>
+  </si>
+  <si>
+    <t>-0.0383</t>
+  </si>
+  <si>
+    <t>0.0445</t>
+  </si>
+  <si>
+    <t>1.1933</t>
+  </si>
+  <si>
+    <t>-38.6177</t>
+  </si>
+  <si>
+    <t>-1137.8602 +0.0476*B + 0.0*C -0.0194*D +0.0014*E +0.0025*F + 0.0*G -0.0787*H -0.1586*I +0.0263*J +0.2091*K +7.913*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-1137.8602</t>
+  </si>
+  <si>
+    <t>0.0476</t>
+  </si>
+  <si>
+    <t>-0.0194</t>
+  </si>
+  <si>
+    <t>0.0014</t>
+  </si>
+  <si>
+    <t>-0.0787</t>
+  </si>
+  <si>
+    <t>-0.1586</t>
+  </si>
+  <si>
+    <t>0.0263</t>
+  </si>
+  <si>
+    <t>0.2091</t>
+  </si>
+  <si>
+    <t>7.9130</t>
+  </si>
+  <si>
+    <t>-1526.1728 +0.1469*B + 0.0*C +0.6096*D -0.0023*E +0.0892*F + 0.0*G -2.8368*H -0.1323*I +0.0153*J +0.9168*K -1.4559*L -171.0237*M</t>
+  </si>
+  <si>
+    <t>-1526.1728</t>
+  </si>
+  <si>
+    <t>0.1469</t>
+  </si>
+  <si>
+    <t>0.6096</t>
+  </si>
+  <si>
+    <t>-0.0023</t>
+  </si>
+  <si>
+    <t>0.0892</t>
+  </si>
+  <si>
+    <t>-2.8368</t>
+  </si>
+  <si>
+    <t>-0.1323</t>
+  </si>
+  <si>
+    <t>0.0153</t>
+  </si>
+  <si>
+    <t>0.9168</t>
+  </si>
+  <si>
+    <t>-1.4559</t>
+  </si>
+  <si>
+    <t>-171.0237</t>
+  </si>
+  <si>
+    <t>-1020.3068 +0.0096*B + 0.0*C -0.5194*D -0.0083*E +0.0376*F + 0.0*G +1.0019*H +0.0684*I +0.0009*J +0.089*K +1.995*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-1020.3068</t>
+  </si>
+  <si>
+    <t>0.0096</t>
+  </si>
+  <si>
+    <t>-0.5194</t>
+  </si>
+  <si>
+    <t>-0.0083</t>
+  </si>
+  <si>
+    <t>0.0376</t>
+  </si>
+  <si>
+    <t>1.0019</t>
+  </si>
+  <si>
+    <t>0.0684</t>
+  </si>
+  <si>
+    <t>0.0890</t>
+  </si>
+  <si>
+    <t>1.9950</t>
+  </si>
+  <si>
+    <t>-1483.9756 +0.0205*B + 0.0*C +1.2307*D +0.0185*E +0.2684*F + 0.0*G -2.625*H +0.0914*I +0.0139*J +0.0713*K +4.6247*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-1483.9756</t>
+  </si>
+  <si>
+    <t>0.0205</t>
+  </si>
+  <si>
+    <t>1.2307</t>
+  </si>
+  <si>
+    <t>0.0185</t>
+  </si>
+  <si>
+    <t>0.2684</t>
+  </si>
+  <si>
+    <t>-2.6250</t>
+  </si>
+  <si>
+    <t>0.0139</t>
+  </si>
+  <si>
+    <t>0.0713</t>
+  </si>
+  <si>
+    <t>4.6247</t>
+  </si>
+  <si>
+    <t>-439.5491 +0.0285*B + 0.0*C +0.9712*D +0.047*E +0.0025*F + 0.0*G -0.5241*H +0.0914*I +0.0259*J -0.6466*K +8.0662*L -108.8896*M</t>
+  </si>
+  <si>
+    <t>-439.5491</t>
+  </si>
+  <si>
+    <t>0.0285</t>
+  </si>
+  <si>
+    <t>0.9712</t>
+  </si>
+  <si>
+    <t>0.0470</t>
+  </si>
+  <si>
+    <t>-0.5241</t>
+  </si>
+  <si>
+    <t>0.0259</t>
+  </si>
+  <si>
+    <t>8.0662</t>
+  </si>
+  <si>
+    <t>-108.8896</t>
+  </si>
+  <si>
+    <t>-2257.9061 +0.0512*B + 0.0*C +0.0429*D -0.0206*E +0.0493*F + 0.0*G +0.5466*H -0.0482*I +0.0488*J +0.5457*K +0.6615*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-2257.9061</t>
+  </si>
+  <si>
+    <t>0.0512</t>
+  </si>
+  <si>
+    <t>0.0429</t>
+  </si>
+  <si>
+    <t>-0.0206</t>
+  </si>
+  <si>
+    <t>0.0493</t>
+  </si>
+  <si>
+    <t>0.5466</t>
+  </si>
+  <si>
+    <t>-0.0482</t>
+  </si>
+  <si>
+    <t>0.0488</t>
+  </si>
+  <si>
+    <t>0.5457</t>
+  </si>
+  <si>
+    <t>0.6615</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0012*B + 0.0*C +0.9118*D -0.0177*E +0.2292*F + 0.0*G +0.0121*H +0.0914*I +0.0591*J +0.786*K +0.2021*L -144.1073*M</t>
+  </si>
+  <si>
+    <t>0.9118</t>
+  </si>
+  <si>
+    <t>-0.0177</t>
+  </si>
+  <si>
+    <t>0.2292</t>
+  </si>
+  <si>
+    <t>0.0121</t>
+  </si>
+  <si>
+    <t>0.0591</t>
+  </si>
+  <si>
+    <t>0.7860</t>
+  </si>
+  <si>
+    <t>0.2021</t>
+  </si>
+  <si>
+    <t>-144.1073</t>
+  </si>
+  <si>
+    <t>-942.7869 +0.0469*B + 0.0*C +0.0689*D -0.0319*E +0.4199*F + 0.0*G -2.3371*H +0.0466*I +0.0009*J +0.4227*K -1.0026*L -54.9676*M</t>
+  </si>
+  <si>
+    <t>-942.7869</t>
+  </si>
+  <si>
+    <t>0.0469</t>
+  </si>
+  <si>
+    <t>0.0689</t>
+  </si>
+  <si>
+    <t>-0.0319</t>
+  </si>
+  <si>
+    <t>0.4199</t>
+  </si>
+  <si>
+    <t>-2.3371</t>
+  </si>
+  <si>
+    <t>0.0466</t>
+  </si>
+  <si>
+    <t>0.4227</t>
+  </si>
+  <si>
+    <t>-1.0026</t>
+  </si>
+  <si>
+    <t>-54.9676</t>
+  </si>
+  <si>
+    <t>-1882.4661 +0.0012*B + 0.0*C +0.4379*D -0.0242*E +0.1349*F + 0.0*G +2.0942*H +0.0914*I +0.0506*J +0.9549*K +10.4546*L -98.4111*M</t>
+  </si>
+  <si>
+    <t>-1882.4661</t>
+  </si>
+  <si>
+    <t>0.4379</t>
+  </si>
+  <si>
+    <t>-0.0242</t>
+  </si>
+  <si>
+    <t>0.1349</t>
+  </si>
+  <si>
+    <t>2.0942</t>
+  </si>
+  <si>
+    <t>0.0506</t>
+  </si>
+  <si>
+    <t>0.9549</t>
+  </si>
+  <si>
+    <t>10.4546</t>
+  </si>
+  <si>
+    <t>-98.4111</t>
+  </si>
+  <si>
+    <t>-130.1478 +0.0012*B + 0.0*C +0.762*D -0.0084*E +0.2121*F + 0.0*G +1.3167*H +0.0914*I +0.0111*J +0.3891*K +9.2046*L -76.5574*M</t>
+  </si>
+  <si>
+    <t>-130.1478</t>
+  </si>
+  <si>
+    <t>0.7620</t>
+  </si>
+  <si>
+    <t>-0.0084</t>
+  </si>
+  <si>
+    <t>0.2121</t>
+  </si>
+  <si>
+    <t>1.3167</t>
+  </si>
+  <si>
+    <t>0.0111</t>
+  </si>
+  <si>
+    <t>0.3891</t>
+  </si>
+  <si>
+    <t>9.2046</t>
+  </si>
+  <si>
+    <t>-76.5574</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0598*B + 0.0*C +0.3609*D -0.0436*E +0.1864*F + 0.0*G +1.1089*H -0.1116*I +0.0009*J +0.4686*K +4.1629*L -78.8732*M</t>
+  </si>
+  <si>
+    <t>0.0598</t>
+  </si>
+  <si>
+    <t>0.3609</t>
+  </si>
+  <si>
+    <t>-0.0436</t>
+  </si>
+  <si>
+    <t>0.1864</t>
+  </si>
+  <si>
+    <t>1.1089</t>
+  </si>
+  <si>
+    <t>-0.1116</t>
+  </si>
+  <si>
+    <t>0.4686</t>
+  </si>
+  <si>
+    <t>4.1629</t>
+  </si>
+  <si>
+    <t>-78.8732</t>
+  </si>
+  <si>
+    <t>-1362.2462 +0.01*B + 0.0*C -0.4753*D -0.0006*E +0.0025*F + 0.0*G -3.2687*H -0.031*I +0.0615*J +2.0418*K -1.5569*L -14.5446*M</t>
+  </si>
+  <si>
+    <t>-1362.2462</t>
+  </si>
+  <si>
+    <t>-0.4753</t>
+  </si>
+  <si>
+    <t>-0.0006</t>
+  </si>
+  <si>
+    <t>-3.2687</t>
+  </si>
+  <si>
+    <t>-0.0310</t>
+  </si>
+  <si>
+    <t>0.0615</t>
+  </si>
+  <si>
+    <t>2.0418</t>
+  </si>
+  <si>
+    <t>-14.5446</t>
+  </si>
+  <si>
+    <t>-76.7181 +0.0623*B + 0.0*C +1.318*D -0.016*E +0.0996*F + 0.0*G -0.6773*H +0.0106*I +0.0009*J -0.0486*K -1.5569*L -68.2552*M</t>
+  </si>
+  <si>
+    <t>-76.7181</t>
+  </si>
+  <si>
+    <t>0.0623</t>
+  </si>
+  <si>
+    <t>1.3180</t>
+  </si>
+  <si>
+    <t>-0.0160</t>
+  </si>
+  <si>
+    <t>0.0996</t>
+  </si>
+  <si>
+    <t>-0.6773</t>
+  </si>
+  <si>
+    <t>0.0106</t>
+  </si>
+  <si>
+    <t>-0.0486</t>
+  </si>
+  <si>
+    <t>-68.2552</t>
+  </si>
+  <si>
+    <t>-331.8245 +0.0174*B + 0.0*C +0.995*D -0.0167*E +0.4078*F + 0.0*G -1.2936*H -0.0094*I +0.0041*J +0.2984*K +6.8679*L -78.6357*M</t>
+  </si>
+  <si>
+    <t>-331.8245</t>
+  </si>
+  <si>
+    <t>0.0174</t>
+  </si>
+  <si>
+    <t>0.9950</t>
+  </si>
+  <si>
+    <t>-0.0167</t>
+  </si>
+  <si>
+    <t>0.4078</t>
+  </si>
+  <si>
+    <t>-1.2936</t>
+  </si>
+  <si>
+    <t>-0.0094</t>
+  </si>
+  <si>
+    <t>0.0041</t>
+  </si>
+  <si>
+    <t>0.2984</t>
+  </si>
+  <si>
+    <t>6.8679</t>
+  </si>
+  <si>
+    <t>-78.6357</t>
+  </si>
+  <si>
+    <t>-935.4904 +0.0565*B + 0.0*C +1.185*D -0.0207*E +0.2391*F + 0.0*G -3.9005*H -0.0174*I +0.0009*J +0.9016*K -1.5569*L -63.9093*M</t>
+  </si>
+  <si>
+    <t>-935.4904</t>
+  </si>
+  <si>
+    <t>0.0565</t>
+  </si>
+  <si>
+    <t>1.1850</t>
+  </si>
+  <si>
+    <t>-0.0207</t>
+  </si>
+  <si>
+    <t>0.2391</t>
+  </si>
+  <si>
+    <t>-3.9005</t>
+  </si>
+  <si>
+    <t>-0.0174</t>
+  </si>
+  <si>
+    <t>0.9016</t>
+  </si>
+  <si>
+    <t>-63.9093</t>
+  </si>
+  <si>
+    <t>-2189.7983 +0.0361*B + 0.0*C -0.1821*D +0.0581*E +0.1663*F + 0.0*G -2.2958*H +0.0265*I +0.0009*J -0.6466*K +4.0727*L -256.1451*M</t>
+  </si>
+  <si>
+    <t>-2189.7983</t>
+  </si>
+  <si>
+    <t>0.0361</t>
+  </si>
+  <si>
+    <t>-0.1821</t>
+  </si>
+  <si>
+    <t>0.0581</t>
+  </si>
+  <si>
+    <t>0.1663</t>
+  </si>
+  <si>
+    <t>-2.2958</t>
+  </si>
+  <si>
+    <t>0.0265</t>
+  </si>
+  <si>
+    <t>4.0727</t>
+  </si>
+  <si>
+    <t>-256.1451</t>
+  </si>
+  <si>
+    <t>-528.9982 +0.0237*B + 0.0*C +1.256*D -0.0216*E +0.2749*F + 0.0*G -0.9255*H -0.0626*I +0.0107*J +0.2236*K +3.0766*L -48.0636*M</t>
+  </si>
+  <si>
+    <t>-528.9982</t>
+  </si>
+  <si>
+    <t>0.0237</t>
+  </si>
+  <si>
+    <t>1.2560</t>
+  </si>
+  <si>
+    <t>-0.0216</t>
+  </si>
+  <si>
+    <t>0.2749</t>
+  </si>
+  <si>
+    <t>-0.9255</t>
+  </si>
+  <si>
+    <t>-0.0626</t>
+  </si>
+  <si>
+    <t>0.0107</t>
+  </si>
+  <si>
+    <t>0.2236</t>
+  </si>
+  <si>
+    <t>3.0766</t>
+  </si>
+  <si>
+    <t>-48.0636</t>
+  </si>
+  <si>
+    <t>-3194.0762 +0.0562*B + 0.0*C +0.0967*D -0.0401*E +0.1092*F + 0.0*G -1.9789*H -0.0484*I +0.0141*J -0.3699*K +3.637*L -149.2999*M</t>
+  </si>
+  <si>
+    <t>-3194.0762</t>
+  </si>
+  <si>
+    <t>0.0562</t>
+  </si>
+  <si>
+    <t>0.0967</t>
+  </si>
+  <si>
+    <t>-0.0401</t>
+  </si>
+  <si>
+    <t>0.1092</t>
+  </si>
+  <si>
+    <t>-1.9789</t>
+  </si>
+  <si>
+    <t>-0.0484</t>
+  </si>
+  <si>
+    <t>0.0141</t>
+  </si>
+  <si>
+    <t>-0.3699</t>
+  </si>
+  <si>
+    <t>3.6370</t>
+  </si>
+  <si>
+    <t>-149.2999</t>
+  </si>
+  <si>
+    <t>-226.7715 +0.0012*B + 0.0*C +0.4213*D -0.025*E +0.0736*F + 0.0*G +1.5473*H -0.0977*I +0.0249*J +0.9666*K +9.0985*L -163.5485*M</t>
+  </si>
+  <si>
+    <t>-226.7715</t>
+  </si>
+  <si>
+    <t>0.4213</t>
+  </si>
+  <si>
+    <t>-0.0250</t>
+  </si>
+  <si>
+    <t>0.0736</t>
+  </si>
+  <si>
+    <t>1.5473</t>
+  </si>
+  <si>
+    <t>-0.0977</t>
+  </si>
+  <si>
+    <t>0.0249</t>
+  </si>
+  <si>
+    <t>0.9666</t>
+  </si>
+  <si>
+    <t>9.0985</t>
+  </si>
+  <si>
+    <t>-163.5485</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0012*B + 0.0*C -0.6918*D +0.0238*E +0.0199*F + 0.0*G -0.3248*H +0.082*I +0.0509*J +0.2757*K +1.6412*L -104.2113*M</t>
+  </si>
+  <si>
+    <t>-0.6918</t>
+  </si>
+  <si>
+    <t>0.0238</t>
+  </si>
+  <si>
+    <t>0.0199</t>
+  </si>
+  <si>
+    <t>-0.3248</t>
+  </si>
+  <si>
+    <t>0.0820</t>
+  </si>
+  <si>
+    <t>0.0509</t>
+  </si>
+  <si>
+    <t>0.2757</t>
+  </si>
+  <si>
+    <t>1.6412</t>
+  </si>
+  <si>
+    <t>-104.2113</t>
+  </si>
+  <si>
+    <t>-770.372 +0.0647*B + 0.0*C -1.3466*D -0.0175*E +0.2796*F + 0.0*G +0.4278*H -0.2743*I +0.0388*J +0.3485*K -1.2489*L -167.9488*M</t>
+  </si>
+  <si>
+    <t>-770.3720</t>
+  </si>
+  <si>
+    <t>0.0647</t>
+  </si>
+  <si>
+    <t>-1.3466</t>
+  </si>
+  <si>
+    <t>-0.0175</t>
+  </si>
+  <si>
+    <t>0.2796</t>
+  </si>
+  <si>
+    <t>0.4278</t>
+  </si>
+  <si>
+    <t>-0.2743</t>
+  </si>
+  <si>
+    <t>0.0388</t>
+  </si>
+  <si>
+    <t>0.3485</t>
+  </si>
+  <si>
+    <t>-1.2489</t>
+  </si>
+  <si>
+    <t>-167.9488</t>
+  </si>
+  <si>
+    <t>-1487.0931 +0.0195*B + 0.0*C +1.1422*D -0.0338*E +0.0025*F + 0.0*G -2.1138*H -0.0927*I +0.0009*J +1.1187*K +2.8159*L -3.6909*M</t>
+  </si>
+  <si>
+    <t>-1487.0931</t>
+  </si>
+  <si>
+    <t>0.0195</t>
+  </si>
+  <si>
+    <t>1.1422</t>
+  </si>
+  <si>
+    <t>-0.0338</t>
+  </si>
+  <si>
+    <t>-2.1138</t>
+  </si>
+  <si>
+    <t>-0.0927</t>
+  </si>
+  <si>
+    <t>1.1187</t>
+  </si>
+  <si>
+    <t>2.8159</t>
+  </si>
+  <si>
+    <t>-3.6909</t>
+  </si>
+  <si>
+    <t>-58.4678 +0.0344*B + 0.0*C +0.0109*D -0.0439*E +0.0715*F + 0.0*G -0.8546*H +0.0162*I +0.0373*J +1.0761*K -1.4259*L -73.4231*M</t>
+  </si>
+  <si>
+    <t>-58.4678</t>
+  </si>
+  <si>
+    <t>0.0344</t>
+  </si>
+  <si>
+    <t>0.0109</t>
+  </si>
+  <si>
+    <t>-0.0439</t>
+  </si>
+  <si>
+    <t>0.0715</t>
+  </si>
+  <si>
+    <t>-0.8546</t>
+  </si>
+  <si>
+    <t>0.0162</t>
+  </si>
+  <si>
+    <t>0.0373</t>
+  </si>
+  <si>
+    <t>1.0761</t>
+  </si>
+  <si>
+    <t>-1.4259</t>
+  </si>
+  <si>
+    <t>-73.4231</t>
+  </si>
+  <si>
+    <t>-305.6827 +0.0314*B + 0.0*C +1.3446*D -0.0172*E +0.3784*F + 0.0*G -1.0952*H -0.1122*I +0.0009*J +0.823*K +8.3919*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-305.6827</t>
+  </si>
+  <si>
+    <t>0.0314</t>
+  </si>
+  <si>
+    <t>1.3446</t>
+  </si>
+  <si>
+    <t>-0.0172</t>
+  </si>
+  <si>
+    <t>0.3784</t>
+  </si>
+  <si>
+    <t>-1.0952</t>
+  </si>
+  <si>
+    <t>-0.1122</t>
+  </si>
+  <si>
+    <t>0.8230</t>
+  </si>
+  <si>
+    <t>8.3919</t>
+  </si>
+  <si>
+    <t>-1041.1636 +0.0554*B + 0.0*C -0.2907*D +0.0198*E +0.0025*F + 0.0*G -1.2467*H -0.2517*I +0.0083*J -0.4131*K +2.1135*L -5.4906*M</t>
+  </si>
+  <si>
+    <t>-1041.1636</t>
+  </si>
+  <si>
+    <t>0.0554</t>
+  </si>
+  <si>
+    <t>-0.2907</t>
+  </si>
+  <si>
+    <t>0.0198</t>
+  </si>
+  <si>
+    <t>-1.2467</t>
+  </si>
+  <si>
+    <t>-0.2517</t>
+  </si>
+  <si>
+    <t>0.0083</t>
+  </si>
+  <si>
+    <t>-0.4131</t>
+  </si>
+  <si>
+    <t>2.1135</t>
+  </si>
+  <si>
+    <t>-5.4906</t>
+  </si>
+  <si>
+    <t>-746.3299 +0.0425*B + 0.0*C +0.0937*D +0.014*E +0.3376*F + 0.0*G -2.7751*H +0.0792*I +0.0355*J +0.9706*K +3.9601*L -190.5131*M</t>
+  </si>
+  <si>
+    <t>-746.3299</t>
+  </si>
+  <si>
+    <t>0.0425</t>
+  </si>
+  <si>
+    <t>0.0937</t>
+  </si>
+  <si>
+    <t>0.0140</t>
+  </si>
+  <si>
+    <t>-2.7751</t>
+  </si>
+  <si>
+    <t>0.0792</t>
+  </si>
+  <si>
+    <t>0.0355</t>
+  </si>
+  <si>
+    <t>0.9706</t>
+  </si>
+  <si>
+    <t>3.9601</t>
+  </si>
+  <si>
+    <t>-190.5131</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0207*B + 0.0*C +0.5362*D -0.0673*E +0.2782*F + 0.0*G +0.6263*H +0.0914*I +0.0441*J +0.2199*K +9.7023*L -198.3637*M</t>
+  </si>
+  <si>
+    <t>0.0207</t>
+  </si>
+  <si>
+    <t>0.5362</t>
+  </si>
+  <si>
+    <t>-0.0673</t>
+  </si>
+  <si>
+    <t>0.2782</t>
+  </si>
+  <si>
+    <t>0.6263</t>
+  </si>
+  <si>
+    <t>0.0441</t>
+  </si>
+  <si>
+    <t>0.2199</t>
+  </si>
+  <si>
+    <t>9.7023</t>
+  </si>
+  <si>
+    <t>-198.3637</t>
+  </si>
+  <si>
+    <t>162.2266 +0.1337*B + 0.0*C +0.9706*D -0.0325*E +0.1689*F + 0.0*G +0.3802*H -0.005*I +0.0323*J +0.9905*K +0.6002*L -53.4976*M</t>
+  </si>
+  <si>
+    <t>0.1337</t>
+  </si>
+  <si>
+    <t>-0.0325</t>
+  </si>
+  <si>
+    <t>0.1689</t>
+  </si>
+  <si>
+    <t>0.3802</t>
+  </si>
+  <si>
+    <t>-0.0050</t>
+  </si>
+  <si>
+    <t>0.0323</t>
+  </si>
+  <si>
+    <t>0.9905</t>
+  </si>
+  <si>
+    <t>0.6002</t>
+  </si>
+  <si>
+    <t>-53.4976</t>
+  </si>
+  <si>
+    <t>-829.7298 +0.037*B + 0.0*C +0.8571*D -0.0582*E +0.1648*F + 0.0*G +1.9496*H -0.1026*I +0.0009*J -0.118*K +5.6953*L -237.6077*M</t>
+  </si>
+  <si>
+    <t>-829.7298</t>
+  </si>
+  <si>
+    <t>0.0370</t>
+  </si>
+  <si>
+    <t>0.8571</t>
+  </si>
+  <si>
+    <t>-0.0582</t>
+  </si>
+  <si>
+    <t>0.1648</t>
+  </si>
+  <si>
+    <t>1.9496</t>
+  </si>
+  <si>
+    <t>-0.1026</t>
+  </si>
+  <si>
+    <t>-0.1180</t>
+  </si>
+  <si>
+    <t>5.6953</t>
+  </si>
+  <si>
+    <t>-237.6077</t>
+  </si>
+  <si>
+    <t>-460.2414 +0.0012*B + 0.0*C +1.5397*D -0.0123*E +0.3857*F + 0.0*G -1.5334*H -0.0159*I +0.067*J -0.3326*K +6.6555*L -278.9213*M</t>
+  </si>
+  <si>
+    <t>-460.2414</t>
+  </si>
+  <si>
+    <t>1.5397</t>
+  </si>
+  <si>
+    <t>-0.0123</t>
+  </si>
+  <si>
+    <t>0.3857</t>
+  </si>
+  <si>
+    <t>-1.5334</t>
+  </si>
+  <si>
+    <t>-0.0159</t>
+  </si>
+  <si>
+    <t>0.0670</t>
+  </si>
+  <si>
+    <t>-0.3326</t>
+  </si>
+  <si>
+    <t>6.6555</t>
+  </si>
+  <si>
+    <t>-278.9213</t>
+  </si>
+  <si>
+    <t>-3840.0714 +0.053*B + 0.0*C +0.322*D -0.023*E +0.1425*F + 0.0*G -1.4716*H -0.0124*I +0.0335*J +0.9392*K +2.76*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-3840.0714</t>
+  </si>
+  <si>
+    <t>0.0530</t>
+  </si>
+  <si>
+    <t>0.3220</t>
+  </si>
+  <si>
+    <t>-0.0230</t>
+  </si>
+  <si>
+    <t>0.1425</t>
+  </si>
+  <si>
+    <t>-1.4716</t>
+  </si>
+  <si>
+    <t>-0.0124</t>
+  </si>
+  <si>
+    <t>0.0335</t>
+  </si>
+  <si>
+    <t>0.9392</t>
+  </si>
+  <si>
+    <t>2.7600</t>
+  </si>
+  <si>
+    <t>97.1843 +0.043*B + 0.0*C -0.1316*D -0.0793*E +0.1103*F + 0.0*G -1.0447*H -0.2586*I +0.0339*J +0.3187*K -1.5569*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>97.1843</t>
+  </si>
+  <si>
+    <t>0.0430</t>
+  </si>
+  <si>
+    <t>-0.1316</t>
+  </si>
+  <si>
+    <t>-0.0793</t>
+  </si>
+  <si>
+    <t>0.1103</t>
+  </si>
+  <si>
+    <t>-1.0447</t>
+  </si>
+  <si>
+    <t>-0.2586</t>
+  </si>
+  <si>
+    <t>0.3187</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0695*B + 0.0*C -0.6694*D +0.0029*E +0.0025*F + 0.0*G -5.0199*H -0.1198*I +0.011*J +1.6988*K +4.0703*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>0.0695</t>
+  </si>
+  <si>
+    <t>-0.6694</t>
+  </si>
+  <si>
+    <t>0.0029</t>
+  </si>
+  <si>
+    <t>-5.0199</t>
+  </si>
+  <si>
+    <t>-0.1198</t>
+  </si>
+  <si>
+    <t>0.0110</t>
+  </si>
+  <si>
+    <t>1.6988</t>
+  </si>
+  <si>
+    <t>4.0703</t>
+  </si>
+  <si>
+    <t>-1255.9731 +0.0606*B + 0.0*C -0.6377*D +0.0173*E +0.0025*F + 0.0*G +1.3476*H -0.063*I +0.0033*J -0.3348*K +6.3552*L -154.2612*M</t>
+  </si>
+  <si>
+    <t>-1255.9731</t>
+  </si>
+  <si>
+    <t>0.0606</t>
+  </si>
+  <si>
+    <t>-0.6377</t>
+  </si>
+  <si>
+    <t>0.0173</t>
+  </si>
+  <si>
+    <t>1.3476</t>
+  </si>
+  <si>
+    <t>-0.0630</t>
+  </si>
+  <si>
+    <t>0.0033</t>
+  </si>
+  <si>
+    <t>-0.3348</t>
+  </si>
+  <si>
+    <t>6.3552</t>
+  </si>
+  <si>
+    <t>-154.2612</t>
+  </si>
+  <si>
+    <t>-384.0729 +0.0118*B + 0.0*C +0.4241*D -0.0101*E +0.0326*F + 0.0*G -2.2037*H -0.2212*I +0.0268*J +0.405*K +10.42*L -52.8556*M</t>
+  </si>
+  <si>
+    <t>-384.0729</t>
+  </si>
+  <si>
+    <t>0.0118</t>
+  </si>
+  <si>
+    <t>0.4241</t>
+  </si>
+  <si>
+    <t>-0.0101</t>
+  </si>
+  <si>
+    <t>0.0326</t>
+  </si>
+  <si>
+    <t>-2.2037</t>
+  </si>
+  <si>
+    <t>-0.2212</t>
+  </si>
+  <si>
+    <t>0.0268</t>
+  </si>
+  <si>
+    <t>0.4050</t>
+  </si>
+  <si>
+    <t>10.4200</t>
+  </si>
+  <si>
+    <t>-52.8556</t>
+  </si>
+  <si>
+    <t>-2853.1212 +0.0787*B + 0.0*C -0.6499*D +0.0081*E +0.0613*F + 0.0*G +0.4922*H -0.075*I +0.0009*J -0.2855*K -1.2913*L -135.8826*M</t>
+  </si>
+  <si>
+    <t>-2853.1212</t>
+  </si>
+  <si>
+    <t>0.0787</t>
+  </si>
+  <si>
+    <t>-0.6499</t>
+  </si>
+  <si>
+    <t>0.0081</t>
+  </si>
+  <si>
+    <t>0.0613</t>
+  </si>
+  <si>
+    <t>0.4922</t>
+  </si>
+  <si>
+    <t>-0.0750</t>
+  </si>
+  <si>
+    <t>-0.2855</t>
+  </si>
+  <si>
+    <t>-1.2913</t>
+  </si>
+  <si>
+    <t>-135.8826</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0344*B + 0.0*C +0.4539*D +0.0212*E +0.0025*F + 0.0*G -1.7947*H -0.1353*I +0.0014*J +1.4141*K +0.8067*L -184.9411*M</t>
+  </si>
+  <si>
+    <t>0.4539</t>
+  </si>
+  <si>
+    <t>0.0212</t>
+  </si>
+  <si>
+    <t>-1.7947</t>
+  </si>
+  <si>
+    <t>-0.1353</t>
+  </si>
+  <si>
+    <t>1.4141</t>
+  </si>
+  <si>
+    <t>0.8067</t>
+  </si>
+  <si>
+    <t>-184.9411</t>
+  </si>
+  <si>
+    <t>-1080.9711 +0.0075*B + 0.0*C -0.6089*D +0.0036*E +0.0025*F + 0.0*G -0.2951*H +0.0914*I +0.0669*J +1.3006*K +1.8322*L -76.6547*M</t>
+  </si>
+  <si>
+    <t>-1080.9711</t>
+  </si>
+  <si>
+    <t>0.0075</t>
+  </si>
+  <si>
+    <t>-0.6089</t>
+  </si>
+  <si>
+    <t>0.0036</t>
+  </si>
+  <si>
+    <t>-0.2951</t>
+  </si>
+  <si>
+    <t>0.0669</t>
+  </si>
+  <si>
+    <t>1.3006</t>
+  </si>
+  <si>
+    <t>1.8322</t>
+  </si>
+  <si>
+    <t>-76.6547</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0639*B + 0.0*C -0.4623*D -0.0662*E +0.0624*F + 0.0*G +1.7585*H -0.0613*I +0.0009*J -0.1857*K +5.6283*L -20.9497*M</t>
+  </si>
+  <si>
+    <t>0.0639</t>
+  </si>
+  <si>
+    <t>-0.4623</t>
+  </si>
+  <si>
+    <t>-0.0662</t>
+  </si>
+  <si>
+    <t>0.0624</t>
+  </si>
+  <si>
+    <t>1.7585</t>
+  </si>
+  <si>
+    <t>-0.0613</t>
+  </si>
+  <si>
+    <t>-0.1857</t>
+  </si>
+  <si>
+    <t>5.6283</t>
+  </si>
+  <si>
+    <t>-20.9497</t>
+  </si>
+  <si>
+    <t>-1057.7162 +0.036*B + 0.0*C +0.0096*D -0.0141*E +0.0025*F + 0.0*G -2.6834*H -0.1434*I +0.0051*J -0.3716*K +4.9832*L -14.6059*M</t>
+  </si>
+  <si>
+    <t>-1057.7162</t>
+  </si>
+  <si>
+    <t>-0.0141</t>
+  </si>
+  <si>
+    <t>-2.6834</t>
+  </si>
+  <si>
+    <t>-0.1434</t>
+  </si>
+  <si>
+    <t>0.0051</t>
+  </si>
+  <si>
+    <t>-0.3716</t>
+  </si>
+  <si>
+    <t>4.9832</t>
+  </si>
+  <si>
+    <t>-14.6059</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0272*B + 0.0*C -0.2816*D -0.0342*E +0.0025*F + 0.0*G -0.3709*H -0.2151*I +0.0374*J +0.6403*K +5.1709*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>0.0272</t>
+  </si>
+  <si>
+    <t>-0.2816</t>
+  </si>
+  <si>
+    <t>-0.0342</t>
+  </si>
+  <si>
+    <t>-0.3709</t>
+  </si>
+  <si>
+    <t>-0.2151</t>
+  </si>
+  <si>
+    <t>0.0374</t>
+  </si>
+  <si>
+    <t>0.6403</t>
+  </si>
+  <si>
+    <t>5.1709</t>
+  </si>
+  <si>
+    <t>-861.2125 +0.0278*B + 0.0*C -0.4041*D -0.0293*E +0.0589*F + 0.0*G +0.0972*H -0.0857*I +0.0248*J +0.4529*K +1.1182*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-861.2125</t>
+  </si>
+  <si>
+    <t>0.0278</t>
+  </si>
+  <si>
+    <t>-0.4041</t>
+  </si>
+  <si>
+    <t>-0.0293</t>
+  </si>
+  <si>
+    <t>0.0589</t>
+  </si>
+  <si>
+    <t>0.0972</t>
+  </si>
+  <si>
+    <t>-0.0857</t>
+  </si>
+  <si>
+    <t>0.0248</t>
+  </si>
+  <si>
+    <t>0.4529</t>
+  </si>
+  <si>
+    <t>1.1182</t>
+  </si>
+  <si>
+    <t>-569.7074 +0.0571*B + 0.0*C -1.3994*D -0.0187*E +0.1947*F + 0.0*G +0.6815*H -0.166*I +0.0312*J -0.6466*K +0.3446*L -86.2762*M</t>
+  </si>
+  <si>
+    <t>-569.7074</t>
+  </si>
+  <si>
+    <t>0.0571</t>
+  </si>
+  <si>
+    <t>-1.3994</t>
+  </si>
+  <si>
+    <t>-0.0187</t>
+  </si>
+  <si>
+    <t>0.1947</t>
+  </si>
+  <si>
+    <t>0.6815</t>
+  </si>
+  <si>
+    <t>-0.1660</t>
+  </si>
+  <si>
+    <t>0.0312</t>
+  </si>
+  <si>
+    <t>0.3446</t>
+  </si>
+  <si>
+    <t>-86.2762</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0294*B + 0.0*C +1.5567*D -0.0651*E +0.0025*F + 0.0*G -0.3717*H -0.1764*I +0.0384*J -0.3334*K +6.4977*L -153.6399*M</t>
+  </si>
+  <si>
+    <t>0.0294</t>
+  </si>
+  <si>
+    <t>1.5567</t>
+  </si>
+  <si>
+    <t>-0.0651</t>
+  </si>
+  <si>
+    <t>-0.3717</t>
+  </si>
+  <si>
+    <t>-0.1764</t>
+  </si>
+  <si>
+    <t>0.0384</t>
+  </si>
+  <si>
+    <t>-0.3334</t>
+  </si>
+  <si>
+    <t>6.4977</t>
+  </si>
+  <si>
+    <t>-153.6399</t>
+  </si>
+  <si>
+    <t>-1271.7064 +0.0649*B + 0.0*C -0.3326*D +0.0001*E +0.156*F + 0.0*G -0.8248*H +0.0914*I +0.0293*J +0.2459*K +2.9775*L -177.4427*M</t>
+  </si>
+  <si>
+    <t>-1271.7064</t>
+  </si>
+  <si>
+    <t>0.0001</t>
+  </si>
+  <si>
+    <t>0.1560</t>
+  </si>
+  <si>
+    <t>-0.8248</t>
+  </si>
+  <si>
+    <t>0.0293</t>
+  </si>
+  <si>
+    <t>0.2459</t>
+  </si>
+  <si>
+    <t>2.9775</t>
+  </si>
+  <si>
+    <t>-177.4427</t>
+  </si>
+  <si>
+    <t>-336.6903 +0.0489*B + 0.0*C +1.0288*D +0.0364*E +0.2204*F + 0.0*G -2.4848*H -0.0222*I +0.0059*J -0.1553*K -0.3119*L -60.7827*M</t>
+  </si>
+  <si>
+    <t>-336.6903</t>
+  </si>
+  <si>
+    <t>0.0489</t>
+  </si>
+  <si>
+    <t>1.0288</t>
+  </si>
+  <si>
+    <t>0.0364</t>
+  </si>
+  <si>
+    <t>0.2204</t>
+  </si>
+  <si>
+    <t>-2.4848</t>
+  </si>
+  <si>
+    <t>-0.0222</t>
+  </si>
+  <si>
+    <t>0.0059</t>
+  </si>
+  <si>
+    <t>-0.1553</t>
+  </si>
+  <si>
+    <t>-0.3119</t>
+  </si>
+  <si>
+    <t>-60.7827</t>
+  </si>
+  <si>
+    <t>-1720.4916 +0.0401*B + 0.0*C -1.2185*D -0.0828*E +0.1162*F + 0.0*G -2.9978*H -0.1262*I +0.0009*J -0.6466*K +3.692*L -114.9084*M</t>
+  </si>
+  <si>
+    <t>-1720.4916</t>
+  </si>
+  <si>
+    <t>0.0401</t>
+  </si>
+  <si>
+    <t>-1.2185</t>
+  </si>
+  <si>
+    <t>-0.0828</t>
+  </si>
+  <si>
+    <t>0.1162</t>
+  </si>
+  <si>
+    <t>-2.9978</t>
+  </si>
+  <si>
+    <t>-0.1262</t>
+  </si>
+  <si>
+    <t>3.6920</t>
+  </si>
+  <si>
+    <t>-114.9084</t>
+  </si>
+  <si>
+    <t>-788.0701 +0.0286*B + 0.0*C -0.3094*D +0.0274*E +0.2081*F + 0.0*G +2.0942*H +0.0914*I +0.0317*J +0.299*K +0.2026*L -136.1359*M</t>
+  </si>
+  <si>
+    <t>-788.0701</t>
+  </si>
+  <si>
+    <t>0.0286</t>
+  </si>
+  <si>
+    <t>-0.3094</t>
+  </si>
+  <si>
+    <t>0.0274</t>
+  </si>
+  <si>
+    <t>0.2081</t>
+  </si>
+  <si>
+    <t>0.0317</t>
+  </si>
+  <si>
+    <t>0.2990</t>
+  </si>
+  <si>
+    <t>0.2026</t>
+  </si>
+  <si>
+    <t>-136.1359</t>
+  </si>
+  <si>
+    <t>-568.3933 +0.0626*B + 0.0*C -0.5814*D -0.0112*E +0.0025*F + 0.0*G -0.5319*H +0.0187*I +0.038*J +0.4933*K +0.0072*L -102.4667*M</t>
+  </si>
+  <si>
+    <t>-568.3933</t>
+  </si>
+  <si>
+    <t>0.0626</t>
+  </si>
+  <si>
+    <t>-0.5814</t>
+  </si>
+  <si>
+    <t>-0.0112</t>
+  </si>
+  <si>
+    <t>-0.5319</t>
+  </si>
+  <si>
+    <t>0.0380</t>
+  </si>
+  <si>
+    <t>0.4933</t>
+  </si>
+  <si>
+    <t>0.0072</t>
+  </si>
+  <si>
+    <t>-102.4667</t>
+  </si>
+  <si>
+    <t>-710.3906 +0.0227*B + 0.0*C +0.5521*D -0.0047*E +0.3237*F + 0.0*G -2.7476*H -0.0157*I +0.0009*J +0.1448*K -1.5569*L -62.6558*M</t>
+  </si>
+  <si>
+    <t>-710.3906</t>
+  </si>
+  <si>
+    <t>0.0227</t>
+  </si>
+  <si>
+    <t>0.5521</t>
+  </si>
+  <si>
+    <t>-0.0047</t>
+  </si>
+  <si>
+    <t>0.3237</t>
+  </si>
+  <si>
+    <t>-2.7476</t>
+  </si>
+  <si>
+    <t>-0.0157</t>
+  </si>
+  <si>
+    <t>0.1448</t>
+  </si>
+  <si>
+    <t>-62.6558</t>
+  </si>
+  <si>
+    <t>-2477.1958 +0.0018*B + 0.0*C +2.1712*D +0.0052*E +0.3127*F + 0.0*G -1.9412*H +0.0914*I +0.0112*J -0.0326*K +4.962*L -52.7572*M</t>
+  </si>
+  <si>
+    <t>-2477.1958</t>
+  </si>
+  <si>
+    <t>0.0018</t>
+  </si>
+  <si>
+    <t>2.1712</t>
+  </si>
+  <si>
+    <t>0.0052</t>
+  </si>
+  <si>
+    <t>0.3127</t>
+  </si>
+  <si>
+    <t>-1.9412</t>
+  </si>
+  <si>
+    <t>0.0112</t>
+  </si>
+  <si>
+    <t>-0.0326</t>
+  </si>
+  <si>
+    <t>4.9620</t>
+  </si>
+  <si>
+    <t>-52.7572</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0012*B + 0.0*C -0.3531*D -0.0222*E +0.1614*F + 0.0*G -1.3821*H -0.0617*I +0.011*J +0.8955*K +0.3222*L -105.493*M</t>
+  </si>
+  <si>
+    <t>-0.3531</t>
+  </si>
+  <si>
+    <t>0.1614</t>
+  </si>
+  <si>
+    <t>-1.3821</t>
+  </si>
+  <si>
+    <t>-0.0617</t>
+  </si>
+  <si>
+    <t>0.8955</t>
+  </si>
+  <si>
+    <t>0.3222</t>
+  </si>
+  <si>
+    <t>-105.4930</t>
+  </si>
+  <si>
+    <t>-648.0844 +0.0264*B + 0.0*C +0.4846*D -0.0422*E +0.1604*F + 0.0*G -0.9473*H -0.166*I +0.0009*J +0.4186*K +2.1052*L -73.0728*M</t>
+  </si>
+  <si>
+    <t>-648.0844</t>
+  </si>
+  <si>
+    <t>0.4846</t>
+  </si>
+  <si>
+    <t>-0.0422</t>
+  </si>
+  <si>
+    <t>0.1604</t>
+  </si>
+  <si>
+    <t>-0.9473</t>
+  </si>
+  <si>
+    <t>0.4186</t>
+  </si>
+  <si>
+    <t>2.1052</t>
+  </si>
+  <si>
+    <t>-73.0728</t>
+  </si>
+  <si>
+    <t>-1194.5515 +0.0752*B + 0.0*C -0.6002*D -0.0121*E +0.0552*F + 0.0*G -3.7795*H -0.0402*I +0.0009*J +0.7917*K +6.1576*L -29.8768*M</t>
+  </si>
+  <si>
+    <t>-1194.5515</t>
+  </si>
+  <si>
+    <t>0.0752</t>
+  </si>
+  <si>
+    <t>-0.6002</t>
+  </si>
+  <si>
+    <t>-0.0121</t>
+  </si>
+  <si>
+    <t>0.0552</t>
+  </si>
+  <si>
+    <t>-3.7795</t>
+  </si>
+  <si>
+    <t>0.7917</t>
+  </si>
+  <si>
+    <t>6.1576</t>
+  </si>
+  <si>
+    <t>-29.8768</t>
+  </si>
+  <si>
+    <t>-99.5097 +0.0145*B + 0.0*C +0.8529*D +0.0124*E +0.3422*F + 0.0*G +1.2096*H -0.2398*I +0.0242*J -0.6466*K +6.7855*L -127.7407*M</t>
+  </si>
+  <si>
+    <t>-99.5097</t>
+  </si>
+  <si>
+    <t>0.0145</t>
+  </si>
+  <si>
+    <t>0.8529</t>
+  </si>
+  <si>
+    <t>0.0124</t>
+  </si>
+  <si>
+    <t>0.3422</t>
+  </si>
+  <si>
+    <t>1.2096</t>
+  </si>
+  <si>
+    <t>-0.2398</t>
+  </si>
+  <si>
+    <t>0.0242</t>
+  </si>
+  <si>
+    <t>6.7855</t>
+  </si>
+  <si>
+    <t>-127.7407</t>
+  </si>
+  <si>
+    <t>-377.8168 +0.0141*B + 0.0*C +0.6058*D +0.0063*E +0.0025*F + 0.0*G -1.4856*H -0.0908*I +0.0334*J +0.1606*K +1.937*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-377.8168</t>
+  </si>
+  <si>
+    <t>0.6058</t>
+  </si>
+  <si>
+    <t>-1.4856</t>
+  </si>
+  <si>
+    <t>-0.0908</t>
+  </si>
+  <si>
+    <t>0.0334</t>
+  </si>
+  <si>
+    <t>0.1606</t>
+  </si>
+  <si>
+    <t>1.9370</t>
+  </si>
+  <si>
+    <t>-3771.7307 +0.0489*B + 0.0*C +0.3485*D +0.0082*E +0.3059*F + 0.0*G +1.1925*H -0.1659*I +0.0418*J +0.6157*K +0.201*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-3771.7307</t>
+  </si>
+  <si>
+    <t>0.3059</t>
+  </si>
+  <si>
+    <t>1.1925</t>
+  </si>
+  <si>
+    <t>-0.1659</t>
+  </si>
+  <si>
+    <t>0.0418</t>
+  </si>
+  <si>
+    <t>0.6157</t>
+  </si>
+  <si>
+    <t>0.2010</t>
+  </si>
+  <si>
+    <t>-2501.2708 +0.0518*B + 0.0*C +0.1634*D +0.0231*E +0.0276*F + 0.0*G -1.3081*H -0.0953*I +0.0094*J -0.6171*K +2.6399*L -139.6216*M</t>
+  </si>
+  <si>
+    <t>-2501.2708</t>
+  </si>
+  <si>
+    <t>0.0518</t>
+  </si>
+  <si>
+    <t>0.1634</t>
+  </si>
+  <si>
+    <t>0.0231</t>
+  </si>
+  <si>
+    <t>0.0276</t>
+  </si>
+  <si>
+    <t>-1.3081</t>
+  </si>
+  <si>
+    <t>-0.0953</t>
+  </si>
+  <si>
+    <t>0.0094</t>
+  </si>
+  <si>
+    <t>-0.6171</t>
+  </si>
+  <si>
+    <t>2.6399</t>
+  </si>
+  <si>
+    <t>-139.6216</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0565*B + 0.0*C -0.7944*D -0.0102*E +0.1713*F + 0.0*G -1.8761*H +0.0914*I +0.0177*J +0.5989*K +0.9742*L -0.7283*M</t>
+  </si>
+  <si>
+    <t>-0.7944</t>
+  </si>
+  <si>
+    <t>-0.0102</t>
+  </si>
+  <si>
+    <t>0.1713</t>
+  </si>
+  <si>
+    <t>-1.8761</t>
+  </si>
+  <si>
+    <t>0.0177</t>
+  </si>
+  <si>
+    <t>0.5989</t>
+  </si>
+  <si>
+    <t>0.9742</t>
+  </si>
+  <si>
+    <t>-0.7283</t>
+  </si>
+  <si>
+    <t>162.2266 +0.0099*B + 0.0*C +0.5881*D -0.0024*E +0.2472*F + 0.0*G -0.7051*H -0.2744*I +0.0009*J +0.6509*K -1.5569*L -2.1809*M</t>
+  </si>
+  <si>
+    <t>0.0099</t>
+  </si>
+  <si>
+    <t>0.5881</t>
+  </si>
+  <si>
+    <t>-0.0024</t>
+  </si>
+  <si>
+    <t>0.2472</t>
+  </si>
+  <si>
+    <t>-0.7051</t>
+  </si>
+  <si>
+    <t>-0.2744</t>
+  </si>
+  <si>
+    <t>0.6509</t>
+  </si>
+  <si>
+    <t>-2.1809</t>
+  </si>
+  <si>
+    <t>-392.8636 +0.0434*B + 0.0*C +0.777*D -0.0116*E +0.2583*F + 0.0*G -2.3895*H -0.0224*I +0.0198*J -0.3265*K +1.9017*L +0.0921*M</t>
+  </si>
+  <si>
+    <t>-392.8636</t>
+  </si>
+  <si>
+    <t>0.0434</t>
+  </si>
+  <si>
+    <t>0.7770</t>
+  </si>
+  <si>
+    <t>-0.0116</t>
+  </si>
+  <si>
+    <t>0.2583</t>
+  </si>
+  <si>
+    <t>-2.3895</t>
+  </si>
+  <si>
+    <t>-0.0224</t>
+  </si>
+  <si>
+    <t>-0.3265</t>
+  </si>
+  <si>
+    <t>1.9017</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1837,22 +4556,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{406723B9-5960-40EF-8FB2-6A3A7EEA858C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2154,7 +4875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="9.23046875" style="2"/>
@@ -4090,8 +6811,3768 @@
         <v>466</v>
       </c>
     </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="E64" s="3">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="E65" s="3">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E67" s="3">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="I71" s="3">
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="E73" s="3">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="I74" s="3">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="E75" s="3">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="I75" s="3">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="E77" s="3">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="I77" s="3">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="I78" s="3">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E79" s="3">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E80" s="3">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="E82" s="3">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="E84" s="3">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="I84" s="3">
+        <v>0</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="E86" s="3">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="E87" s="3">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="E88" s="3">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E90" s="3">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E92" s="3">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I92" s="3">
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E93" s="3">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I93" s="3">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E95" s="3">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I95" s="3">
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="E97" s="3">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E98" s="3">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I98" s="3">
+        <v>0</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E99" s="3">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I99" s="3">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E103" s="3">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I103" s="3">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E104" s="3">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I104" s="3">
+        <v>0</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E105" s="3">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I105" s="3">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E106" s="3">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I106" s="3">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O106" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E107" s="3">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I107" s="3">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="O107" s="2" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E108" s="3">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="I108" s="3">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E109" s="3">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I109" s="3">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O109" s="2" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E110" s="3">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I110" s="3">
+        <v>0</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="N110" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O110" s="2" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E111" s="3">
+        <v>0</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I111" s="3">
+        <v>0</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="N111" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E112" s="3">
+        <v>0</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="I112" s="3">
+        <v>0</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="N112" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E113" s="3">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="I113" s="3">
+        <v>0</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E114" s="3">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="I114" s="3">
+        <v>0</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E115" s="3">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I115" s="3">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="E116" s="3">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I116" s="3">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="N116" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E117" s="3">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I117" s="3">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="M117" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="N117" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="O117" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E118" s="3">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I118" s="3">
+        <v>0</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="N118" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="O118" s="2" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="E119" s="3">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="I119" s="3">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="O119" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E120" s="3">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I120" s="3">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="O120" s="2" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E121" s="3">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I121" s="3">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="O121" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>